--- a/results/reliability_eval/Llama-3-8B_P103_sample_30_tokens_0.1_temp_factual_retrieval_scores_08-24-4.xlsx
+++ b/results/reliability_eval/Llama-3-8B_P103_sample_30_tokens_0.1_temp_factual_retrieval_scores_08-24-4.xlsx
@@ -477,31 +477,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.430831180915406</v>
+        <v>0.5270265183595882</v>
       </c>
       <c r="B2" t="n">
-        <v>0.7080891455101976</v>
+        <v>0.8141589196436086</v>
       </c>
       <c r="C2" t="n">
-        <v>0.430831180915406</v>
+        <v>0.5269951505341941</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7080894911497013</v>
+        <v>0.8141445127259831</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5710324654142536</v>
+        <v>0.4535285666785864</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7887788210503414</v>
+        <v>0.7702059684473079</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9905641206637468</v>
+        <v>0.9859817188313602</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9960130440863281</v>
+        <v>0.9957117772113214</v>
       </c>
       <c r="I2" t="n">
-        <v>0.751</v>
+        <v>0.801</v>
       </c>
     </row>
   </sheetData>
